--- a/VerveStacks_MAR_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_MAR_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MAR_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{138341E0-8811-4777-934A-CB98893A8E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D02DCE91-57CC-4754-AA7C-1768CEED9DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2F84BFCE-7279-4953-AAE6-3E56FD580630}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6971DC21-6CC4-46F3-864B-444C60B6782F}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -622,7 +622,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC6CD83C-8F0E-4F40-9AE3-693FB55794C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF58EA5-C54D-4889-AF12-F752A1579FB8}">
   <dimension ref="B3:L25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
